--- a/device-model-indicators/星敏_指标库_20260225.xlsx
+++ b/device-model-indicators/星敏_指标库_20260225.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="237" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="297" uniqueCount="62">
   <si>
     <t>型号 Model</t>
   </si>
@@ -2174,15 +2174,9 @@
       <c r="B38" s="0">
         <v>0.12</v>
       </c>
-      <c r="C38" s="0">
-        <v>110</v>
-      </c>
-      <c r="D38" s="0">
-        <v>45</v>
-      </c>
-      <c r="E38" s="0">
-        <v>45</v>
-      </c>
+      <c r="C38" s="0"/>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
       <c r="F38" s="0"/>
       <c r="G38" s="0"/>
       <c r="H38" s="0">
@@ -2191,42 +2185,28 @@
       <c r="I38" s="0">
         <v>24</v>
       </c>
-      <c r="J38" s="0">
-        <v>3</v>
-      </c>
-      <c r="K38" s="0">
-        <v>3</v>
-      </c>
+      <c r="J38" s="0"/>
+      <c r="K38" s="0"/>
       <c r="L38" s="0">
         <v>10</v>
       </c>
-      <c r="M38" s="0">
-        <v>15</v>
-      </c>
-      <c r="N38" s="0">
-        <v>18</v>
-      </c>
+      <c r="M38" s="0"/>
+      <c r="N38" s="0"/>
       <c r="O38" s="0">
         <v>5.7999999999999998</v>
       </c>
       <c r="P38" s="0">
         <v>30</v>
       </c>
-      <c r="Q38" s="0">
-        <v>25</v>
-      </c>
+      <c r="Q38" s="0"/>
       <c r="R38" s="0">
         <v>1</v>
       </c>
       <c r="S38" s="0">
         <v>5</v>
       </c>
-      <c r="T38" s="0">
-        <v>-30</v>
-      </c>
-      <c r="U38" s="0">
-        <v>50</v>
-      </c>
+      <c r="T38" s="0"/>
+      <c r="U38" s="0"/>
       <c r="V38" s="0">
         <v>8</v>
       </c>
@@ -2235,53 +2215,25 @@
       <c r="A39" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="B39" s="0">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="C39" s="0">
-        <v>120</v>
-      </c>
-      <c r="D39" s="0">
-        <v>50</v>
-      </c>
-      <c r="E39" s="0">
-        <v>50</v>
-      </c>
+      <c r="B39" s="0"/>
+      <c r="C39" s="0"/>
+      <c r="D39" s="0"/>
+      <c r="E39" s="0"/>
       <c r="F39" s="0"/>
       <c r="G39" s="0"/>
       <c r="H39" s="0">
         <v>2</v>
       </c>
-      <c r="I39" s="0">
-        <v>18</v>
-      </c>
-      <c r="J39" s="0">
-        <v>3</v>
-      </c>
-      <c r="K39" s="0">
-        <v>3</v>
-      </c>
-      <c r="L39" s="0">
-        <v>10</v>
-      </c>
-      <c r="M39" s="0">
-        <v>15</v>
-      </c>
-      <c r="N39" s="0">
-        <v>18</v>
-      </c>
-      <c r="O39" s="0">
-        <v>5.7999999999999998</v>
-      </c>
-      <c r="P39" s="0">
-        <v>30</v>
-      </c>
-      <c r="Q39" s="0">
-        <v>25</v>
-      </c>
-      <c r="R39" s="0">
-        <v>1.2</v>
-      </c>
+      <c r="I39" s="0"/>
+      <c r="J39" s="0"/>
+      <c r="K39" s="0"/>
+      <c r="L39" s="0"/>
+      <c r="M39" s="0"/>
+      <c r="N39" s="0"/>
+      <c r="O39" s="0"/>
+      <c r="P39" s="0"/>
+      <c r="Q39" s="0"/>
+      <c r="R39" s="0"/>
       <c r="S39" s="0">
         <v>5</v>
       </c>

--- a/device-model-indicators/星敏_指标库_20260225.xlsx
+++ b/device-model-indicators/星敏_指标库_20260225.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="297" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="357" uniqueCount="62">
   <si>
     <t>型号 Model</t>
   </si>
@@ -1264,7 +1264,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>0.55000000000000004</v>
+        <v>0.55000000000000005</v>
       </c>
       <c r="C21" s="0"/>
       <c r="D21" s="0"/>
@@ -2172,7 +2172,7 @@
         <v>60</v>
       </c>
       <c r="B38" s="0">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C38" s="0"/>
       <c r="D38" s="0"/>
@@ -2180,10 +2180,10 @@
       <c r="F38" s="0"/>
       <c r="G38" s="0"/>
       <c r="H38" s="0">
-        <v>2.3999999999999999</v>
+        <v>3</v>
       </c>
       <c r="I38" s="0">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J38" s="0"/>
       <c r="K38" s="0"/>
@@ -2196,11 +2196,11 @@
         <v>5.7999999999999998</v>
       </c>
       <c r="P38" s="0">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q38" s="0"/>
       <c r="R38" s="0">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="S38" s="0">
         <v>5</v>
@@ -2208,7 +2208,7 @@
       <c r="T38" s="0"/>
       <c r="U38" s="0"/>
       <c r="V38" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -2222,7 +2222,7 @@
       <c r="F39" s="0"/>
       <c r="G39" s="0"/>
       <c r="H39" s="0">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I39" s="0"/>
       <c r="J39" s="0"/>
@@ -2244,7 +2244,7 @@
         <v>50</v>
       </c>
       <c r="V39" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
